--- a/examples/HFP_jon+jane.xlsx
+++ b/examples/HFP_jon+jane.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,35 +449,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>net inv</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -491,13 +496,16 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -507,13 +515,16 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -523,13 +534,16 @@
       <c r="C4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -539,13 +553,16 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -555,13 +572,16 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -574,16 +594,19 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>2000</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>7000</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -596,16 +619,19 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>2000</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -618,16 +644,19 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>2000</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>7000</v>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -640,16 +669,19 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>2000</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -662,16 +694,19 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>2000</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>7000</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -681,13 +716,16 @@
       <c r="C12" t="n">
         <v>0</v>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -697,13 +735,16 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -713,13 +754,16 @@
       <c r="C14" t="n">
         <v>0</v>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -729,13 +773,16 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -745,13 +792,16 @@
       <c r="C16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -761,13 +811,16 @@
       <c r="C17" t="n">
         <v>0</v>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -777,13 +830,16 @@
       <c r="C18" t="n">
         <v>0</v>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -793,13 +849,16 @@
       <c r="C19" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -809,13 +868,16 @@
       <c r="C20" t="n">
         <v>0</v>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -825,13 +887,16 @@
       <c r="C21" t="n">
         <v>0</v>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -841,13 +906,16 @@
       <c r="C22" t="n">
         <v>0</v>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -857,13 +925,16 @@
       <c r="C23" t="n">
         <v>0</v>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -873,13 +944,16 @@
       <c r="C24" t="n">
         <v>0</v>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -889,13 +963,16 @@
       <c r="C25" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -905,13 +982,16 @@
       <c r="C26" t="n">
         <v>0</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -921,13 +1001,16 @@
       <c r="C27" t="n">
         <v>0</v>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -937,13 +1020,16 @@
       <c r="C28" t="n">
         <v>0</v>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -953,13 +1039,16 @@
       <c r="C29" t="n">
         <v>0</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -969,13 +1058,16 @@
       <c r="C30" t="n">
         <v>0</v>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -985,13 +1077,16 @@
       <c r="C31" t="n">
         <v>0</v>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1001,13 +1096,16 @@
       <c r="C32" t="n">
         <v>0</v>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1017,13 +1115,16 @@
       <c r="C33" t="n">
         <v>0</v>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1033,13 +1134,16 @@
       <c r="C34" t="n">
         <v>0</v>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1049,13 +1153,16 @@
       <c r="C35" t="n">
         <v>0</v>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1065,13 +1172,16 @@
       <c r="C36" t="n">
         <v>0</v>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1084,7 +1194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1105,35 +1215,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>net inv</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -1147,15 +1262,18 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
         <v>6000</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1165,15 +1283,18 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
         <v>6000</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1183,15 +1304,18 @@
       <c r="C4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
         <v>6000</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1201,15 +1325,18 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
         <v>7000</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,15 +1346,18 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
         <v>7500</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1239,15 +1369,18 @@
       <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
         <v>3000</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1259,15 +1392,18 @@
       <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="n">
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
         <v>3000</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1279,15 +1415,18 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="n">
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
         <v>3000</v>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1299,15 +1438,18 @@
       <c r="C10" t="n">
         <v>0</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="n">
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
         <v>3000</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1319,15 +1461,18 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
         <v>3000</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1339,15 +1484,18 @@
       <c r="C12" t="n">
         <v>0</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
         <v>3000</v>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1359,15 +1507,18 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
         <v>3000</v>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1379,15 +1530,18 @@
       <c r="C14" t="n">
         <v>0</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="n">
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
         <v>3000</v>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1397,13 +1551,16 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1413,13 +1570,16 @@
       <c r="C16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1429,13 +1589,16 @@
       <c r="C17" t="n">
         <v>0</v>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1445,13 +1608,16 @@
       <c r="C18" t="n">
         <v>0</v>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1461,13 +1627,16 @@
       <c r="C19" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1477,13 +1646,16 @@
       <c r="C20" t="n">
         <v>0</v>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1493,13 +1665,16 @@
       <c r="C21" t="n">
         <v>0</v>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1509,13 +1684,16 @@
       <c r="C22" t="n">
         <v>0</v>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1525,13 +1703,16 @@
       <c r="C23" t="n">
         <v>0</v>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1541,13 +1722,16 @@
       <c r="C24" t="n">
         <v>0</v>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1557,13 +1741,16 @@
       <c r="C25" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1573,13 +1760,16 @@
       <c r="C26" t="n">
         <v>0</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1589,13 +1779,16 @@
       <c r="C27" t="n">
         <v>0</v>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1605,13 +1798,16 @@
       <c r="C28" t="n">
         <v>0</v>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1621,13 +1817,16 @@
       <c r="C29" t="n">
         <v>0</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1637,13 +1836,16 @@
       <c r="C30" t="n">
         <v>0</v>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1653,13 +1855,16 @@
       <c r="C31" t="n">
         <v>0</v>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1669,13 +1874,16 @@
       <c r="C32" t="n">
         <v>0</v>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1685,13 +1893,16 @@
       <c r="C33" t="n">
         <v>0</v>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1701,13 +1912,16 @@
       <c r="C34" t="n">
         <v>0</v>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1717,13 +1931,16 @@
       <c r="C35" t="n">
         <v>0</v>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1733,13 +1950,16 @@
       <c r="C36" t="n">
         <v>0</v>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1749,13 +1969,16 @@
       <c r="C37" t="n">
         <v>0</v>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1765,13 +1988,16 @@
       <c r="C38" t="n">
         <v>0</v>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1781,13 +2007,16 @@
       <c r="C39" t="n">
         <v>0</v>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/HFP_jon+jane.xlsx
+++ b/examples/HFP_jon+jane.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,11 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>HSA ctrb</t>
         </is>
       </c>
     </row>
@@ -506,6 +511,9 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -525,6 +533,9 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -544,6 +555,9 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -563,6 +577,9 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -582,6 +599,9 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -607,6 +627,9 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -632,6 +655,9 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -657,6 +683,9 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -682,6 +711,9 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -707,6 +739,9 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -726,6 +761,9 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -745,6 +783,9 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -764,6 +805,9 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -783,6 +827,9 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -802,6 +849,9 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -821,6 +871,9 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -840,6 +893,9 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -859,6 +915,9 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -878,6 +937,9 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -897,6 +959,9 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -916,6 +981,9 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -935,6 +1003,9 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -954,6 +1025,9 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -973,6 +1047,9 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -992,6 +1069,9 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1011,6 +1091,9 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1030,6 +1113,9 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1049,6 +1135,9 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1068,6 +1157,9 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1087,6 +1179,9 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1106,6 +1201,9 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1125,6 +1223,9 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1144,6 +1245,9 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1163,6 +1267,9 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1182,6 +1289,9 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1194,7 +1304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,6 +1361,11 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>HSA ctrb</t>
         </is>
       </c>
     </row>
@@ -1274,6 +1389,9 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1295,6 +1413,9 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1316,6 +1437,9 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1337,6 +1461,9 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1358,6 +1485,9 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1381,6 +1511,9 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1537,9 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1427,6 +1563,9 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1450,6 +1589,9 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1473,6 +1615,9 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1496,6 +1641,9 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1519,6 +1667,9 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1542,6 +1693,9 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1561,6 +1715,9 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1580,6 +1737,9 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1599,6 +1759,9 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1618,6 +1781,9 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1637,6 +1803,9 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1656,6 +1825,9 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1675,6 +1847,9 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1694,6 +1869,9 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1713,6 +1891,9 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1732,6 +1913,9 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1751,6 +1935,9 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1770,6 +1957,9 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1789,6 +1979,9 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1808,6 +2001,9 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1827,6 +2023,9 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1846,6 +2045,9 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1865,6 +2067,9 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1884,6 +2089,9 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1903,6 +2111,9 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1922,6 +2133,9 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1941,6 +2155,9 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1960,6 +2177,9 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1979,6 +2199,9 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1998,6 +2221,9 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2017,6 +2243,9 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/HFP_jon+jane.xlsx
+++ b/examples/HFP_jon+jane.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jon" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jane" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Assets" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Jon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Jane" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Debts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fixed Assets" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,66 +416,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>anticipated wages</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>QCD</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -510,8 +503,11 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -532,8 +528,11 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -554,8 +553,11 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -576,8 +578,11 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -598,8 +603,11 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -626,8 +634,11 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -654,8 +665,11 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -682,8 +696,11 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -710,8 +727,11 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -738,8 +758,11 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -760,8 +783,11 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -782,8 +808,11 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -804,8 +833,11 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -826,8 +858,11 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -848,8 +883,11 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -870,8 +908,11 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -892,8 +933,11 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -914,8 +958,11 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -936,8 +983,11 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -958,8 +1008,11 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -980,8 +1033,11 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1002,8 +1058,11 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1024,8 +1083,11 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1046,8 +1108,11 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1068,8 +1133,11 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1090,8 +1158,11 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1112,8 +1183,11 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1134,8 +1208,11 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1156,8 +1233,11 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1178,8 +1258,11 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1200,8 +1283,11 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1222,8 +1308,11 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1244,8 +1333,11 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1266,8 +1358,11 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1288,8 +1383,11 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1304,66 +1402,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>anticipated wages</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>QCD</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -1388,8 +1491,11 @@
         <v>6000</v>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1412,8 +1518,11 @@
         <v>6000</v>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1436,8 +1545,11 @@
         <v>6000</v>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1460,8 +1572,11 @@
         <v>7000</v>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1484,8 +1599,11 @@
         <v>7500</v>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1510,8 +1628,11 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1536,8 +1657,11 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1562,8 +1686,11 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1588,8 +1715,11 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1614,8 +1744,11 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1640,8 +1773,11 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1666,8 +1802,11 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1692,8 +1831,11 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1714,8 +1856,11 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1736,8 +1881,11 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1758,8 +1906,11 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1780,8 +1931,11 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1802,8 +1956,11 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1824,8 +1981,11 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1846,8 +2006,11 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1868,8 +2031,11 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1890,8 +2056,11 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1912,8 +2081,11 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1934,8 +2106,11 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1956,8 +2131,11 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1978,8 +2156,11 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2000,8 +2181,11 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2022,8 +2206,11 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2044,8 +2231,11 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2066,8 +2256,11 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2088,8 +2281,11 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2110,8 +2306,11 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2132,8 +2331,11 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2154,8 +2356,11 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2176,8 +2381,11 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2198,8 +2406,11 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2220,8 +2431,11 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2242,8 +2456,11 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2262,37 +2479,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>term</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
@@ -2313,47 +2530,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>basis</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>yod</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>commission</t>
         </is>

--- a/examples/HFP_jon+jane.xlsx
+++ b/examples/HFP_jon+jane.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,15 +472,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -490,24 +495,16 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -515,24 +512,16 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -540,24 +529,16 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -565,24 +546,16 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -590,24 +563,16 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -630,15 +595,10 @@
       <c r="F7" t="n">
         <v>7000</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -661,15 +621,10 @@
       <c r="F8" t="n">
         <v>7000</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -692,15 +647,10 @@
       <c r="F9" t="n">
         <v>7000</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -723,15 +673,10 @@
       <c r="F10" t="n">
         <v>7000</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -754,15 +699,10 @@
       <c r="F11" t="n">
         <v>7000</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -770,24 +710,16 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -795,24 +727,16 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -820,24 +744,16 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -845,24 +761,16 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -870,24 +778,16 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -895,24 +795,16 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -920,24 +812,16 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -945,24 +829,16 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -970,24 +846,16 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -995,24 +863,16 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1020,24 +880,16 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1045,24 +897,16 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1070,24 +914,16 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1095,24 +931,16 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1120,24 +948,16 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1145,24 +965,16 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1170,24 +982,16 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1195,24 +999,16 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="n">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1220,24 +1016,16 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1245,24 +1033,16 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1270,24 +1050,16 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1295,24 +1067,16 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1320,24 +1084,16 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1345,24 +1101,16 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="n">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1370,24 +1118,16 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="n">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1402,7 +1142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1458,15 +1198,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -1476,26 +1221,19 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>6000</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1503,26 +1241,19 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>6000</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1530,26 +1261,19 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>6000</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1557,26 +1281,19 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>7000</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1584,26 +1301,19 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>7500</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1620,19 +1330,13 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>3000</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1649,19 +1353,13 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>3000</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1678,19 +1376,13 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>3000</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1707,19 +1399,13 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>3000</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1736,19 +1422,13 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
         <v>3000</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1765,19 +1445,13 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
         <v>3000</v>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1794,19 +1468,13 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>3000</v>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1823,19 +1491,13 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
         <v>3000</v>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1843,24 +1505,16 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1868,24 +1522,16 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1893,24 +1539,16 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1918,24 +1556,16 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1943,24 +1573,16 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1968,24 +1590,16 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1993,24 +1607,16 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2018,24 +1624,16 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2043,24 +1641,16 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2068,24 +1658,16 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2093,24 +1675,16 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2118,24 +1692,16 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2143,24 +1709,16 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2168,24 +1726,16 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2193,24 +1743,16 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="n">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2218,24 +1760,16 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2243,24 +1777,16 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2268,24 +1794,16 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2293,24 +1811,16 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2318,24 +1828,16 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2343,24 +1845,16 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="n">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2368,24 +1862,16 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="n">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2393,24 +1879,16 @@
       <c r="A37" t="n">
         <v>2056</v>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="n">
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2418,24 +1896,16 @@
       <c r="A38" t="n">
         <v>2057</v>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2443,24 +1913,16 @@
       <c r="A39" t="n">
         <v>2058</v>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="n">
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
         <v>0</v>
       </c>
     </row>
